--- a/public/templates/forms/A-066-BackupScheduleMediaInventory-FORM.xlsx
+++ b/public/templates/forms/A-066-BackupScheduleMediaInventory-FORM.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backup Schedule" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Media Inventory" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Backup Schedule'!$10:$10</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -748,7 +751,6 @@
       <c r="B23" s="24" t="n"/>
       <c r="C23" s="13">
         <f>COUNTA(A11:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -760,7 +762,6 @@
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="13">
         <f>COUNTIF(F11:F20,"Overdue")</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -772,7 +773,6 @@
       <c r="B25" s="24" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(E11:E20,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -789,7 +789,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="34.7" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>When a scheduled backup fails or an item is overdue, the [IT support role] is alerted, and the failure is recorded and escalated to the [Director / Coordinator] within [one business day].</t>
@@ -944,7 +944,7 @@
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="12" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="34.7" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): list any [BRACKETED] field that could not be resolved from project context, and any decision needing confirmation.</t>
@@ -989,7 +989,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1024,7 +1024,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34.7" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Media / Target ID</t>
@@ -1157,8 +1157,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1191,7 +1191,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, escalation, sign-off and revision history live on the Schedule tab.</t>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Encryption &amp; Immutability</t>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Small (1–5, no in-house IT)</t>
@@ -1565,7 +1565,7 @@
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="22" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -1579,7 +1579,7 @@
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="22" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="34.7" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -1606,6 +1606,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>